--- a/www/terminologies/ASS-A24-ModeExercice-TypeActivite-ENREG.xlsx
+++ b/www/terminologies/ASS-A24-ModeExercice-TypeActivite-ENREG.xlsx
@@ -105,7 +105,7 @@
     <t>Relationship</t>
   </si>
   <si>
-    <t>https://mos.esante.gouv.fr/NOS/TRE_R23-ModeExercice/FHIR/TRE-R23-ModeExercice|20231215120000</t>
+    <t>https://mos.esante.gouv.fr/NOS/TRE_R23-ModeExercice/FHIR/TRE-R23-ModeExercice|20260202120000</t>
   </si>
   <si>
     <t/>

--- a/www/terminologies/ASS-A24-ModeExercice-TypeActivite-ENREG.xlsx
+++ b/www/terminologies/ASS-A24-ModeExercice-TypeActivite-ENREG.xlsx
@@ -105,13 +105,13 @@
     <t>Relationship</t>
   </si>
   <si>
-    <t>https://mos.esante.gouv.fr/NOS/TRE_R23-ModeExercice/FHIR/TRE-R23-ModeExercice|20260202120000</t>
+    <t>https://mos.esante.gouv.fr/NOS/TRE_R23-ModeExercice/FHIR/TRE-R23-ModeExercice</t>
   </si>
   <si>
     <t/>
   </si>
   <si>
-    <t>https://mos.esante.gouv.fr/NOS/TRE_R24-TypeActiviteLiberale/FHIR/TRE-R24-TypeActiviteLiberale|20231215120000</t>
+    <t>https://mos.esante.gouv.fr/NOS/TRE_R24-TypeActiviteLiberale/FHIR/TRE-R24-TypeActiviteLiberale</t>
   </si>
   <si>
     <t>L</t>
